--- a/data_processed/results_OLS_m2_floorarea_per_capitaincome.xlsx
+++ b/data_processed/results_OLS_m2_floorarea_per_capitaincome.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6331" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0.6411" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>141.0579859120641</v>
+        <v>142.9471662408041</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9553884741984817</v>
+        <v>0.9059985828559953</v>
       </c>
       <c r="D3" t="n">
-        <v>1.850514760689246e-127</v>
+        <v>2.633565740766527e-116</v>
       </c>
     </row>
     <row r="4">
@@ -483,11 +483,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-12.13819997671382</v>
+        <v>-19.2329387999918</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -499,14 +499,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.09802800266791092</v>
+        <v>-12.05492255326917</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1160095148997866</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-1.419183352158188</v>
+        <v>-0.1268608630729373</v>
       </c>
       <c r="D6" t="n">
-        <v>6.559274430089903e-23</v>
+        <v>0.03792583472842297</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>distance_supermarket</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.009077222344847541</v>
+        <v>-1.668572821666132</v>
       </c>
       <c r="D7" t="n">
-        <v>2.469807358044319e-150</v>
+        <v>1.599621852049459e-39</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>distance_middleschool</t>
+          <t>distance_supermarket</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.001407223277994435</v>
+        <v>0.01059468022619361</v>
       </c>
       <c r="D8" t="n">
-        <v>1.027764739212294e-25</v>
+        <v>3.219064761674701e-189</v>
       </c>
     </row>
     <row r="9">
@@ -563,14 +563,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>distance_depstore</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-19.21892672575673</v>
+        <v>-0.002077941667109033</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>2.667370113888833e-69</v>
       </c>
     </row>
   </sheetData>
